--- a/backend_api/templates/sampling_certificate_template.xlsx
+++ b/backend_api/templates/sampling_certificate_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aaron Avila\Documents\ERP-SOM\backend_api\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EDD3A09A-A244-4F8A-9B3F-7ABE0C69A3B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:80000009_{6D73F0A6-0C85-4A91-8025-BC8C567BAC1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4415BCC8-AE3E-45DD-8DA0-D66BE456F924}"/>
   </bookViews>
